--- a/src/app/modules/dashboard/excel_files/whole-food-plant-based-quinoa-and-wild-rice-recipes.xlsx
+++ b/src/app/modules/dashboard/excel_files/whole-food-plant-based-quinoa-and-wild-rice-recipes.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9373,7 +9373,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -11939,7 +11939,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -12528,7 +12528,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -13121,7 +13121,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -13210,7 +13210,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -13317,7 +13317,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -13600,7 +13600,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -13904,7 +13904,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -14100,7 +14100,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -14288,7 +14288,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'bowls', 'salads', 'wraps', 'stews']</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
